--- a/output/pdf_financials_xlsx/POW.xlsx
+++ b/output/pdf_financials_xlsx/POW.xlsx
@@ -2275,16 +2275,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3009</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2341</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1904</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="93">
@@ -4364,7 +4364,11 @@
           <t>Reserves 2,249</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -5568,7 +5572,11 @@
           <t>Reserves 2,330</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -6710,7 +6718,11 @@
           <t>Reserves 1,904</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>3009</v>
       </c>

--- a/output/pdf_financials_xlsx/POW.xlsx
+++ b/output/pdf_financials_xlsx/POW.xlsx
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-124</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-115</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -12200,7 +12200,11 @@
           <t>Net loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -13390,7 +13394,11 @@
           <t>Net loss from discontinued operations [Note 4]</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E293" s="5" t="n">
         <v>-32</v>
       </c>
